--- a/dados/PEDIDOSPENDENTES.xlsx
+++ b/dados/PEDIDOSPENDENTES.xlsx
@@ -1,12 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E29003-56EE-4CBB-818E-282552ABE3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="105" WindowWidth="21075" WindowHeight="12585"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Report" r:id="rId3"/>
+    <sheet name="Report" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -369,73 +383,66 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="4">
-    <numFmt formatCode="&quot;R&quot;$#,0.00;(&quot;R&quot;$#,0.00)" numFmtId="164"/>
-    <numFmt formatCode="dd/mmyyyy" numFmtId="165"/>
-    <numFmt formatCode="0\ &quot;%&quot;" numFmtId="166"/>
-    <numFmt formatCode="#,0;-#,0" numFmtId="167"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="&quot;R&quot;\$#,##0.00;\(&quot;R&quot;\$#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="dd/mmyyyy"/>
+    <numFmt numFmtId="166" formatCode="0\ &quot;%&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11"/>
       <charset val="1"/>
-      <color rgb="00000000"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <sz val="16"/>
       <charset val="1"/>
-      <color rgb="00000000"/>
-      <b/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <sz val="10"/>
       <charset val="1"/>
-      <color rgb="00000000"/>
-      <b/>
     </font>
     <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <sz val="8"/>
       <charset val="1"/>
-      <color rgb="00000000"/>
-      <b/>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <sz val="8"/>
       <charset val="1"/>
-      <color rgb="00000000"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <sz val="11"/>
       <charset val="1"/>
-      <color rgb="00000000"/>
-      <b/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <sz val="10"/>
       <charset val="1"/>
-      <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF1F"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -448,60 +455,62 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top" horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="0" applyProtection="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="1" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="2" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="2" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="2" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="3" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="4" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="4" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="4" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" borderId="0" fillId="0" fontId="4" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" borderId="0" fillId="0" fontId="4" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" borderId="0" fillId="0" fontId="4" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" borderId="0" fillId="0" fontId="5" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" borderId="0" fillId="0" fontId="6" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" borderId="0" fillId="0" fontId="6" applyProtection="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="37" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -521,36 +530,406 @@
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="00000000"/>
       <rgbColor rgb="00FFFF1F"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L111"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="6"/>
+  <sheetFormatPr defaultColWidth="6" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" width="89.23828125" min="1" max="1"/>
-    <col customWidth="1" width="31.71484375" min="2" max="2"/>
-    <col customWidth="1" width="36.14453125" min="3" max="3"/>
-    <col customWidth="1" width="13.9921875" min="4" max="4"/>
-    <col customWidth="1" width="11.27734375" min="5" max="5"/>
-    <col customWidth="1" width="11.14453125" min="6" max="6"/>
-    <col customWidth="1" width="9.84765625" min="7" max="7"/>
-    <col customWidth="1" width="10.4296875" min="8" max="8"/>
-    <col customWidth="1" width="12.4296875" min="9" max="9"/>
-    <col customWidth="1" width="16.703125" min="10" max="10"/>
-    <col customWidth="1" width="9.71484375" min="11" max="11"/>
-    <col customWidth="1" width="13.14453125" min="12" max="12"/>
+    <col min="1" max="1" width="89.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" ht="77.35" spans="1:1">
+    <row r="1" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" ht="15" spans="1:12">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -588,12 +967,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" customHeight="1" ht="15" spans="1:1">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" customHeight="1" ht="30.35" spans="1:10">
+    <row r="4" spans="1:12" ht="30.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
@@ -603,29 +982,29 @@
       <c r="C4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="8">
         <v>1100</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="9">
         <v>4.29</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="9">
         <v>4719</v>
       </c>
       <c r="G4" s="10">
         <v>46198</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="11" t="n">
+      <c r="H4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
         <v>0</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" customHeight="1" ht="28.15" spans="1:10">
+    <row r="5" spans="1:12" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -635,29 +1014,29 @@
       <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="8">
         <v>1540</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="9">
         <v>5.3</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="9">
         <v>8162</v>
       </c>
       <c r="G5" s="10">
         <v>46198</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="11" t="n">
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
         <v>0</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" customHeight="1" ht="29.15" spans="1:10">
+    <row r="6" spans="1:12" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
@@ -667,51 +1046,51 @@
       <c r="C6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="8">
         <v>1260</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="9">
         <v>6.08</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="9">
         <v>7660.8</v>
       </c>
       <c r="G6" s="10">
         <v>46198</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="11" t="n">
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" customHeight="1" ht="15" spans="1:5">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="13">
         <v>20541.8</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" ht="15" spans="1:1">
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" customHeight="1" ht="29" spans="1:10">
+    <row r="9" spans="1:12" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -721,29 +1100,29 @@
       <c r="C9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="8">
         <v>900</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="9">
         <v>4.63</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="9">
         <v>4167</v>
       </c>
       <c r="G9" s="10">
         <v>46209</v>
       </c>
-      <c r="H9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="n">
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
         <v>0</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" customHeight="1" ht="29.5" spans="1:10">
+    <row r="10" spans="1:12" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -753,51 +1132,51 @@
       <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="8">
         <v>1050</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>8.46</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="E10" s="9">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="F10" s="9">
         <v>8883</v>
       </c>
       <c r="G10" s="10">
         <v>46209</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="11" t="n">
+      <c r="H10" s="8">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
         <v>0</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" customHeight="1" ht="15" spans="1:5">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="13">
         <v>13050</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" ht="77.35" spans="1:1">
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" customHeight="1" ht="15" spans="1:12">
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
@@ -835,12 +1214,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" customHeight="1" ht="15" spans="1:1">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" customHeight="1" ht="57.1" spans="1:10">
+    <row r="15" spans="1:12" ht="57.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
@@ -850,29 +1229,29 @@
       <c r="C15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="8">
         <v>1100</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="9">
         <v>4.63</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="9">
         <v>5093</v>
       </c>
       <c r="G15" s="10">
         <v>46231</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="11" t="n">
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11">
         <v>0</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customHeight="1" ht="55.3" spans="1:10">
+    <row r="16" spans="1:12" ht="55.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
@@ -882,29 +1261,29 @@
       <c r="C16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="8">
         <v>1100</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="9">
         <v>5.73</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="9">
         <v>6303</v>
       </c>
       <c r="G16" s="10">
         <v>46231</v>
       </c>
-      <c r="H16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="11" t="n">
+      <c r="H16" s="8">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
         <v>0</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customHeight="1" ht="54.45" spans="1:10">
+    <row r="17" spans="1:12" ht="54.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>14</v>
       </c>
@@ -914,29 +1293,29 @@
       <c r="C17" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="8">
         <v>900</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="9">
         <v>6.57</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="9">
         <v>5913</v>
       </c>
       <c r="G17" s="10">
         <v>46231</v>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="11" t="n">
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11">
         <v>0</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" customHeight="1" ht="55.05" spans="1:10">
+    <row r="18" spans="1:12" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
@@ -946,51 +1325,51 @@
       <c r="C18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="8">
         <v>702</v>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>8.46</v>
-      </c>
-      <c r="F18" s="9" t="n">
+      <c r="E18" s="9">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="F18" s="9">
         <v>5938.92</v>
       </c>
       <c r="G18" s="10">
         <v>46231</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="11" t="n">
+      <c r="H18" s="8">
+        <v>0</v>
+      </c>
+      <c r="I18" s="11">
         <v>0</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" customHeight="1" ht="15" spans="1:5">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>23247.92</v>
+      <c r="C19" s="13">
+        <v>23247.919999999998</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" ht="77.35" spans="1:1">
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="21" customHeight="1" ht="15" spans="1:12">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>1</v>
       </c>
@@ -1028,12 +1407,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" customHeight="1" ht="15" spans="1:1">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" customHeight="1" ht="37.05" spans="1:10">
+    <row r="23" spans="1:12" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>14</v>
       </c>
@@ -1043,29 +1422,29 @@
       <c r="C23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="8">
         <v>374</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="9">
         <v>11.12</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="9">
         <v>4158.88</v>
       </c>
       <c r="G23" s="10">
-        <v>46265.7568055556</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="11" t="n">
+        <v>46265.756805555597</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" customHeight="1" ht="36.95" spans="1:10">
+    <row r="24" spans="1:12" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>14</v>
       </c>
@@ -1075,51 +1454,51 @@
       <c r="C24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="8">
         <v>288</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="9">
         <v>15.92</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="9">
         <v>4584.96</v>
       </c>
       <c r="G24" s="10">
-        <v>46265.7568055556</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="11" t="n">
+        <v>46265.756805555597</v>
+      </c>
+      <c r="H24" s="8">
+        <v>0</v>
+      </c>
+      <c r="I24" s="11">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="25" customHeight="1" ht="15" spans="1:5">
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="13">
         <v>8743.84</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" ht="15" spans="1:1">
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" customHeight="1" ht="19.8" spans="1:10">
+    <row r="27" spans="1:12" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>14</v>
       </c>
@@ -1129,29 +1508,29 @@
       <c r="C27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="8">
         <v>600</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="9">
         <v>5.64</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="9">
         <v>3384</v>
       </c>
       <c r="G27" s="10">
-        <v>46269.6939699074</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="11" t="n">
+        <v>46269.693969907399</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="11">
         <v>0</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="28" customHeight="1" ht="20.25" spans="1:10">
+    <row r="28" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>14</v>
       </c>
@@ -1161,29 +1540,29 @@
       <c r="C28" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="8">
         <v>270</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="9">
         <v>7.1</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="9">
         <v>1917</v>
       </c>
       <c r="G28" s="10">
-        <v>46269.6939699074</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="11" t="n">
+        <v>46269.693969907399</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0</v>
+      </c>
+      <c r="I28" s="11">
         <v>0</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" customHeight="1" ht="18.6" spans="1:10">
+    <row r="29" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>14</v>
       </c>
@@ -1193,29 +1572,29 @@
       <c r="C29" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="8">
         <v>450</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="9">
         <v>8.32</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="9">
         <v>3744</v>
       </c>
       <c r="G29" s="10">
-        <v>46269.6939699074</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="11" t="n">
+        <v>46269.693969907399</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="11">
         <v>0</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" customHeight="1" ht="20.5" spans="1:10">
+    <row r="30" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>14</v>
       </c>
@@ -1225,51 +1604,51 @@
       <c r="C30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="8">
         <v>105</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="9">
         <v>5.2</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="9">
         <v>546</v>
       </c>
       <c r="G30" s="10">
-        <v>46269.6939699074</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="11" t="n">
+        <v>46269.693969907399</v>
+      </c>
+      <c r="H30" s="8">
+        <v>0</v>
+      </c>
+      <c r="I30" s="11">
         <v>0</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" customHeight="1" ht="15" spans="1:5">
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="13">
         <v>9591</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" ht="77.35" spans="1:1">
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="33" customHeight="1" ht="15" spans="1:12">
+    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>1</v>
       </c>
@@ -1307,12 +1686,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" customHeight="1" ht="15" spans="1:1">
+    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" customHeight="1" ht="47.15" spans="1:10">
+    <row r="35" spans="1:12" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>14</v>
       </c>
@@ -1322,29 +1701,29 @@
       <c r="C35" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="8">
         <v>270</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="9">
         <v>7.12</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="9">
         <v>1922.4</v>
       </c>
       <c r="G35" s="10">
         <v>46232</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="11" t="n">
+      <c r="H35" s="8">
+        <v>0</v>
+      </c>
+      <c r="I35" s="11">
         <v>0</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="36" customHeight="1" ht="47.85" spans="1:10">
+    <row r="36" spans="1:12" ht="47.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>14</v>
       </c>
@@ -1354,29 +1733,29 @@
       <c r="C36" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="8">
         <v>320</v>
       </c>
-      <c r="E36" s="9" t="n">
-        <v>8.8</v>
-      </c>
-      <c r="F36" s="9" t="n">
+      <c r="E36" s="9">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F36" s="9">
         <v>2816</v>
       </c>
       <c r="G36" s="10">
         <v>46232</v>
       </c>
-      <c r="H36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="11" t="n">
+      <c r="H36" s="8">
+        <v>0</v>
+      </c>
+      <c r="I36" s="11">
         <v>0</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" customHeight="1" ht="47" spans="1:10">
+    <row r="37" spans="1:12" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>14</v>
       </c>
@@ -1386,29 +1765,29 @@
       <c r="C37" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="8">
         <v>70</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="9">
         <v>19.25</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="9">
         <v>1347.5</v>
       </c>
       <c r="G37" s="10">
         <v>46232</v>
       </c>
-      <c r="H37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="11" t="n">
+      <c r="H37" s="8">
+        <v>0</v>
+      </c>
+      <c r="I37" s="11">
         <v>0</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" customHeight="1" ht="46.9" spans="1:10">
+    <row r="38" spans="1:12" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>14</v>
       </c>
@@ -1418,29 +1797,29 @@
       <c r="C38" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="8">
         <v>280</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="9">
         <v>10.41</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="9">
         <v>2914.8</v>
       </c>
       <c r="G38" s="10">
         <v>46232</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="11" t="n">
+      <c r="H38" s="8">
+        <v>0</v>
+      </c>
+      <c r="I38" s="11">
         <v>0</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" customHeight="1" ht="48.35" spans="1:10">
+    <row r="39" spans="1:12" ht="48.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>14</v>
       </c>
@@ -1450,29 +1829,29 @@
       <c r="C39" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="8">
         <v>120</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="9">
         <v>13.36</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="9">
         <v>1603.2</v>
       </c>
       <c r="G39" s="10">
         <v>46232</v>
       </c>
-      <c r="H39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="11" t="n">
+      <c r="H39" s="8">
+        <v>0</v>
+      </c>
+      <c r="I39" s="11">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" customHeight="1" ht="38.4" spans="1:10">
+    <row r="40" spans="1:12" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>14</v>
       </c>
@@ -1482,29 +1861,29 @@
       <c r="C40" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="8">
         <v>90</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="9">
         <v>7.12</v>
       </c>
-      <c r="F40" s="9" t="n">
-        <v>640.8</v>
+      <c r="F40" s="9">
+        <v>640.79999999999995</v>
       </c>
       <c r="G40" s="10">
-        <v>46261.4569444444</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="11" t="n">
+        <v>46261.456944444399</v>
+      </c>
+      <c r="H40" s="8">
+        <v>0</v>
+      </c>
+      <c r="I40" s="11">
         <v>0</v>
       </c>
       <c r="J40" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" customHeight="1" ht="37.4" spans="1:10">
+    <row r="41" spans="1:12" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>14</v>
       </c>
@@ -1514,29 +1893,29 @@
       <c r="C41" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="8">
         <v>80</v>
       </c>
-      <c r="E41" s="9" t="n">
-        <v>8.8</v>
-      </c>
-      <c r="F41" s="9" t="n">
+      <c r="E41" s="9">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F41" s="9">
         <v>704</v>
       </c>
       <c r="G41" s="10">
-        <v>46261.4569444444</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="11" t="n">
+        <v>46261.456944444399</v>
+      </c>
+      <c r="H41" s="8">
+        <v>0</v>
+      </c>
+      <c r="I41" s="11">
         <v>0</v>
       </c>
       <c r="J41" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" customHeight="1" ht="38.25" spans="1:10">
+    <row r="42" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>14</v>
       </c>
@@ -1546,51 +1925,51 @@
       <c r="C42" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="8">
         <v>70</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="9">
         <v>10.41</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="9">
         <v>728.7</v>
       </c>
       <c r="G42" s="10">
-        <v>46261.4569444444</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="11" t="n">
+        <v>46261.456944444399</v>
+      </c>
+      <c r="H42" s="8">
+        <v>0</v>
+      </c>
+      <c r="I42" s="11">
         <v>0</v>
       </c>
       <c r="J42" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" customHeight="1" ht="15" spans="1:5">
+    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="13">
         <v>12677.4</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" ht="77.35" spans="1:1">
+      <c r="E43" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="45" customHeight="1" ht="15" spans="1:12">
+    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>1</v>
       </c>
@@ -1628,12 +2007,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" customHeight="1" ht="15" spans="1:1">
+    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="47" customHeight="1" ht="30.35" spans="1:10">
+    <row r="47" spans="1:12" ht="30.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>14</v>
       </c>
@@ -1643,29 +2022,29 @@
       <c r="C47" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="D47" s="8">
         <v>110</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="9">
         <v>4.29</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="9">
         <v>471.9</v>
       </c>
       <c r="G47" s="10">
         <v>46268</v>
       </c>
-      <c r="H47" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="11" t="n">
+      <c r="H47" s="8">
+        <v>0</v>
+      </c>
+      <c r="I47" s="11">
         <v>0</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="48" customHeight="1" ht="28.15" spans="1:10">
+    <row r="48" spans="1:12" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>14</v>
       </c>
@@ -1675,29 +2054,29 @@
       <c r="C48" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D48" s="8" t="n">
+      <c r="D48" s="8">
         <v>100</v>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" s="9">
         <v>5.81</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="9">
         <v>581</v>
       </c>
       <c r="G48" s="10">
         <v>46268</v>
       </c>
-      <c r="H48" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="11" t="n">
+      <c r="H48" s="8">
+        <v>0</v>
+      </c>
+      <c r="I48" s="11">
         <v>0</v>
       </c>
       <c r="J48" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="49" customHeight="1" ht="29.15" spans="1:10">
+    <row r="49" spans="1:12" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>14</v>
       </c>
@@ -1707,29 +2086,29 @@
       <c r="C49" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="8" t="n">
+      <c r="D49" s="8">
         <v>75</v>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="E49" s="9">
         <v>8.58</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="9">
         <v>643.5</v>
       </c>
       <c r="G49" s="10">
         <v>46268</v>
       </c>
-      <c r="H49" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="11" t="n">
+      <c r="H49" s="8">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11">
         <v>0</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="50" customHeight="1" ht="29.4" spans="1:10">
+    <row r="50" spans="1:12" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>14</v>
       </c>
@@ -1739,51 +2118,51 @@
       <c r="C50" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D50" s="8" t="n">
+      <c r="D50" s="8">
         <v>70</v>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="E50" s="9">
         <v>7.83</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" s="9">
         <v>548.1</v>
       </c>
       <c r="G50" s="10">
         <v>46268</v>
       </c>
-      <c r="H50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="11" t="n">
+      <c r="H50" s="8">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11">
         <v>0</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="51" customHeight="1" ht="15" spans="1:5">
+    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C51" s="13" t="n">
+      <c r="C51" s="13">
         <v>2244.5</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E51" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" ht="15" spans="1:1">
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" customHeight="1" ht="36.6" spans="1:10">
+    <row r="53" spans="1:12" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>14</v>
       </c>
@@ -1793,51 +2172,51 @@
       <c r="C53" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="D53" s="8">
         <v>800</v>
       </c>
-      <c r="E53" s="9" t="n">
+      <c r="E53" s="9">
         <v>5.89</v>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" s="9">
         <v>4712</v>
       </c>
       <c r="G53" s="10">
         <v>46232</v>
       </c>
-      <c r="H53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="11" t="n">
+      <c r="H53" s="8">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11">
         <v>0</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" customHeight="1" ht="15" spans="1:5">
+    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="13" t="n">
+      <c r="C54" s="13">
         <v>4712</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" ht="77.35" spans="1:1">
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="56" customHeight="1" ht="15" spans="1:12">
+    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>1</v>
       </c>
@@ -1875,12 +2254,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" customHeight="1" ht="15" spans="1:1">
+    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="58" customHeight="1" ht="30.35" spans="1:10">
+    <row r="58" spans="1:12" ht="30.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>14</v>
       </c>
@@ -1890,29 +2269,29 @@
       <c r="C58" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D58" s="8" t="n">
+      <c r="D58" s="8">
         <v>550</v>
       </c>
-      <c r="E58" s="9" t="n">
+      <c r="E58" s="9">
         <v>4.29</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="9">
         <v>2359.5</v>
       </c>
       <c r="G58" s="10">
         <v>46234</v>
       </c>
-      <c r="H58" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="11" t="n">
+      <c r="H58" s="8">
+        <v>0</v>
+      </c>
+      <c r="I58" s="11">
         <v>0</v>
       </c>
       <c r="J58" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="59" customHeight="1" ht="28.15" spans="1:10">
+    <row r="59" spans="1:12" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>14</v>
       </c>
@@ -1922,29 +2301,29 @@
       <c r="C59" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D59" s="8" t="n">
+      <c r="D59" s="8">
         <v>540</v>
       </c>
-      <c r="E59" s="9" t="n">
+      <c r="E59" s="9">
         <v>6.08</v>
       </c>
-      <c r="F59" s="9" t="n">
+      <c r="F59" s="9">
         <v>3283.2</v>
       </c>
       <c r="G59" s="10">
         <v>46234</v>
       </c>
-      <c r="H59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="11" t="n">
+      <c r="H59" s="8">
+        <v>0</v>
+      </c>
+      <c r="I59" s="11">
         <v>0</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="60" customHeight="1" ht="29.15" spans="1:10">
+    <row r="60" spans="1:12" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>14</v>
       </c>
@@ -1954,51 +2333,51 @@
       <c r="C60" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D60" s="8" t="n">
+      <c r="D60" s="8">
         <v>1050</v>
       </c>
-      <c r="E60" s="9" t="n">
+      <c r="E60" s="9">
         <v>7.83</v>
       </c>
-      <c r="F60" s="9" t="n">
+      <c r="F60" s="9">
         <v>8221.5</v>
       </c>
       <c r="G60" s="10">
         <v>46234</v>
       </c>
-      <c r="H60" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="11" t="n">
+      <c r="H60" s="8">
+        <v>0</v>
+      </c>
+      <c r="I60" s="11">
         <v>0</v>
       </c>
       <c r="J60" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="61" customHeight="1" ht="15" spans="1:5">
+    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C61" s="13" t="n">
+      <c r="C61" s="13">
         <v>13864.2</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" ht="77.35" spans="1:1">
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="63" customHeight="1" ht="15" spans="1:12">
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>1</v>
       </c>
@@ -2036,12 +2415,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" customHeight="1" ht="15" spans="1:1">
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="65" customHeight="1" ht="57.1" spans="1:10">
+    <row r="65" spans="1:12" ht="57.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>14</v>
       </c>
@@ -2051,51 +2430,51 @@
       <c r="C65" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D65" s="8" t="n">
+      <c r="D65" s="8">
         <v>200100</v>
       </c>
-      <c r="E65" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F65" s="9" t="n">
+      <c r="E65" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F65" s="9">
         <v>820410</v>
       </c>
       <c r="G65" s="10">
         <v>46119</v>
       </c>
-      <c r="H65" s="8" t="n">
+      <c r="H65" s="8">
         <v>147450</v>
       </c>
-      <c r="I65" s="11" t="n">
+      <c r="I65" s="11">
         <v>73.69</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="66" customHeight="1" ht="15" spans="1:5">
+    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="13" t="n">
+      <c r="C66" s="13">
         <v>820410</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E66" s="14" t="n">
+      <c r="E66" s="14">
         <v>147450</v>
       </c>
     </row>
-    <row r="67" customHeight="1" ht="15" spans="1:1">
+    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="68" customHeight="1" ht="27.95" spans="1:10">
+    <row r="68" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>14</v>
       </c>
@@ -2105,51 +2484,51 @@
       <c r="C68" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D68" s="8" t="n">
+      <c r="D68" s="8">
         <v>50100</v>
       </c>
-      <c r="E68" s="9" t="n">
-        <v>4.517</v>
-      </c>
-      <c r="F68" s="9" t="n">
+      <c r="E68" s="9">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="F68" s="9">
         <v>226301.7</v>
       </c>
       <c r="G68" s="10">
         <v>46163</v>
       </c>
-      <c r="H68" s="8" t="n">
+      <c r="H68" s="8">
         <v>22200</v>
       </c>
-      <c r="I68" s="11" t="n">
+      <c r="I68" s="11">
         <v>44.31</v>
       </c>
       <c r="J68" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="69" customHeight="1" ht="15" spans="1:5">
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="13" t="n">
+      <c r="C69" s="13">
         <v>226301.7</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="14" t="n">
+      <c r="E69" s="14">
         <v>22200</v>
       </c>
     </row>
-    <row r="70" customHeight="1" ht="77.35" spans="1:1">
+    <row r="70" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="71" customHeight="1" ht="15" spans="1:12">
+    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>1</v>
       </c>
@@ -2187,12 +2566,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" customHeight="1" ht="15" spans="1:1">
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="73" customHeight="1" ht="20.4" spans="1:10">
+    <row r="73" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>14</v>
       </c>
@@ -2202,51 +2581,51 @@
       <c r="C73" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="8" t="n">
+      <c r="D73" s="8">
         <v>3408</v>
       </c>
-      <c r="E73" s="9" t="n">
+      <c r="E73" s="9">
         <v>44.9</v>
       </c>
-      <c r="F73" s="9" t="n">
-        <v>153019.2</v>
+      <c r="F73" s="9">
+        <v>153019.20000000001</v>
       </c>
       <c r="G73" s="10">
         <v>46162</v>
       </c>
-      <c r="H73" s="8" t="n">
+      <c r="H73" s="8">
         <v>3168</v>
       </c>
-      <c r="I73" s="11" t="n">
+      <c r="I73" s="11">
         <v>92.96</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="74" customHeight="1" ht="15" spans="1:5">
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="13" t="n">
-        <v>153019.2</v>
+      <c r="C74" s="13">
+        <v>153019.20000000001</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E74" s="14" t="n">
+      <c r="E74" s="14">
         <v>3168</v>
       </c>
     </row>
-    <row r="75" customHeight="1" ht="15" spans="1:1">
+    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="76" customHeight="1" ht="18.35" spans="1:10">
+    <row r="76" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>14</v>
       </c>
@@ -2256,51 +2635,51 @@
       <c r="C76" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D76" s="8" t="n">
+      <c r="D76" s="8">
         <v>4008</v>
       </c>
-      <c r="E76" s="9" t="n">
+      <c r="E76" s="9">
         <v>44</v>
       </c>
-      <c r="F76" s="9" t="n">
+      <c r="F76" s="9">
         <v>176352</v>
       </c>
       <c r="G76" s="10">
         <v>46231</v>
       </c>
-      <c r="H76" s="8" t="n">
+      <c r="H76" s="8">
         <v>2856</v>
       </c>
-      <c r="I76" s="11" t="n">
-        <v>71.26</v>
+      <c r="I76" s="11">
+        <v>71.260000000000005</v>
       </c>
       <c r="J76" s="8" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="77" customHeight="1" ht="15" spans="1:5">
+    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="13" t="n">
+      <c r="C77" s="13">
         <v>176352</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="14" t="n">
+      <c r="E77" s="14">
         <v>2856</v>
       </c>
     </row>
-    <row r="78" customHeight="1" ht="15" spans="1:1">
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="79" customHeight="1" ht="37.3" spans="1:10">
+    <row r="79" spans="1:12" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>14</v>
       </c>
@@ -2310,51 +2689,51 @@
       <c r="C79" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D79" s="8" t="n">
+      <c r="D79" s="8">
         <v>1008</v>
       </c>
-      <c r="E79" s="9" t="n">
+      <c r="E79" s="9">
         <v>42</v>
       </c>
-      <c r="F79" s="9" t="n">
+      <c r="F79" s="9">
         <v>42336</v>
       </c>
       <c r="G79" s="10">
         <v>46261.6741666667</v>
       </c>
-      <c r="H79" s="8" t="n">
+      <c r="H79" s="8">
         <v>288</v>
       </c>
-      <c r="I79" s="11" t="n">
+      <c r="I79" s="11">
         <v>28.57</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="80" customHeight="1" ht="15" spans="1:5">
+    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C80" s="13" t="n">
+      <c r="C80" s="13">
         <v>42336</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E80" s="14" t="n">
+      <c r="E80" s="14">
         <v>288</v>
       </c>
     </row>
-    <row r="81" customHeight="1" ht="15" spans="1:1">
+    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="82" customHeight="1" ht="19.55" spans="1:10">
+    <row r="82" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>14</v>
       </c>
@@ -2364,51 +2743,51 @@
       <c r="C82" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D82" s="8" t="n">
+      <c r="D82" s="8">
         <v>1200</v>
       </c>
-      <c r="E82" s="9" t="n">
+      <c r="E82" s="9">
         <v>34.65</v>
       </c>
-      <c r="F82" s="9" t="n">
+      <c r="F82" s="9">
         <v>41580</v>
       </c>
       <c r="G82" s="10">
         <v>46265</v>
       </c>
-      <c r="H82" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="11" t="n">
+      <c r="H82" s="8">
+        <v>0</v>
+      </c>
+      <c r="I82" s="11">
         <v>0</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="83" customHeight="1" ht="15" spans="1:5">
+    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C83" s="13" t="n">
+      <c r="C83" s="13">
         <v>41580</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E83" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" ht="77.35" spans="1:1">
+      <c r="E83" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="85" customHeight="1" ht="15" spans="1:12">
+    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>1</v>
       </c>
@@ -2446,12 +2825,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" customHeight="1" ht="15" spans="1:1">
+    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="87" customHeight="1" ht="30.35" spans="1:10">
+    <row r="87" spans="1:12" ht="30.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>14</v>
       </c>
@@ -2461,51 +2840,51 @@
       <c r="C87" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D87" s="8" t="n">
+      <c r="D87" s="8">
         <v>4000</v>
       </c>
-      <c r="E87" s="9" t="n">
+      <c r="E87" s="9">
         <v>23.5</v>
       </c>
-      <c r="F87" s="9" t="n">
+      <c r="F87" s="9">
         <v>94000</v>
       </c>
       <c r="G87" s="10">
-        <v>46274.9769791667</v>
-      </c>
-      <c r="H87" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="11" t="n">
+        <v>46274.976979166699</v>
+      </c>
+      <c r="H87" s="8">
+        <v>0</v>
+      </c>
+      <c r="I87" s="11">
         <v>0</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="88" customHeight="1" ht="15" spans="1:5">
+    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C88" s="13" t="n">
+      <c r="C88" s="13">
         <v>94000</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" ht="15" spans="1:1">
+      <c r="E88" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="90" customHeight="1" ht="20.4" spans="1:10">
+    <row r="90" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>14</v>
       </c>
@@ -2515,29 +2894,29 @@
       <c r="C90" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D90" s="8" t="n">
+      <c r="D90" s="8">
         <v>1008</v>
       </c>
-      <c r="E90" s="9" t="n">
+      <c r="E90" s="9">
         <v>49.5</v>
       </c>
-      <c r="F90" s="9" t="n">
+      <c r="F90" s="9">
         <v>49896</v>
       </c>
       <c r="G90" s="10">
         <v>46268.4426157407</v>
       </c>
-      <c r="H90" s="8" t="n">
+      <c r="H90" s="8">
         <v>300</v>
       </c>
-      <c r="I90" s="11" t="n">
+      <c r="I90" s="11">
         <v>29.76</v>
       </c>
       <c r="J90" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="91" customHeight="1" ht="19.05" spans="1:10">
+    <row r="91" spans="1:12" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>14</v>
       </c>
@@ -2547,51 +2926,51 @@
       <c r="C91" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D91" s="8" t="n">
+      <c r="D91" s="8">
         <v>204</v>
       </c>
-      <c r="E91" s="9" t="n">
+      <c r="E91" s="9">
         <v>48.5</v>
       </c>
-      <c r="F91" s="9" t="n">
+      <c r="F91" s="9">
         <v>9894</v>
       </c>
       <c r="G91" s="10">
         <v>46268.4426157407</v>
       </c>
-      <c r="H91" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="11" t="n">
+      <c r="H91" s="8">
+        <v>0</v>
+      </c>
+      <c r="I91" s="11">
         <v>0</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="92" customHeight="1" ht="15" spans="1:5">
+    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C92" s="13" t="n">
+      <c r="C92" s="13">
         <v>59790</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="14" t="n">
+      <c r="E92" s="14">
         <v>300</v>
       </c>
     </row>
-    <row r="93" customHeight="1" ht="77.35" spans="1:1">
+    <row r="93" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="94" customHeight="1" ht="15" spans="1:12">
+    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>1</v>
       </c>
@@ -2629,12 +3008,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" customHeight="1" ht="15" spans="1:1">
+    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="96" customHeight="1" ht="20.4" spans="1:10">
+    <row r="96" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>14</v>
       </c>
@@ -2644,51 +3023,51 @@
       <c r="C96" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D96" s="8" t="n">
+      <c r="D96" s="8">
         <v>50000</v>
       </c>
-      <c r="E96" s="9" t="n">
+      <c r="E96" s="9">
         <v>0.36</v>
       </c>
-      <c r="F96" s="9" t="n">
+      <c r="F96" s="9">
         <v>18000</v>
       </c>
       <c r="G96" s="10">
-        <v>46274.4426851852</v>
-      </c>
-      <c r="H96" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="11" t="n">
+        <v>46274.442685185197</v>
+      </c>
+      <c r="H96" s="8">
+        <v>0</v>
+      </c>
+      <c r="I96" s="11">
         <v>0</v>
       </c>
       <c r="J96" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="97" customHeight="1" ht="15" spans="1:5">
+    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C97" s="13" t="n">
+      <c r="C97" s="13">
         <v>18000</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E97" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" ht="77.35" spans="1:1">
+      <c r="E97" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="99" customHeight="1" ht="15" spans="1:12">
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>1</v>
       </c>
@@ -2726,12 +3105,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" customHeight="1" ht="15" spans="1:1">
+    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="101" customHeight="1" ht="30.35" spans="1:10">
+    <row r="101" spans="1:12" ht="30.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>14</v>
       </c>
@@ -2741,51 +3120,51 @@
       <c r="C101" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D101" s="8" t="n">
+      <c r="D101" s="8">
         <v>57000</v>
       </c>
-      <c r="E101" s="9" t="n">
+      <c r="E101" s="9">
         <v>0.39</v>
       </c>
-      <c r="F101" s="9" t="n">
+      <c r="F101" s="9">
         <v>22230</v>
       </c>
       <c r="G101" s="10">
-        <v>46274.6825347222</v>
-      </c>
-      <c r="H101" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="11" t="n">
+        <v>46274.682534722197</v>
+      </c>
+      <c r="H101" s="8">
+        <v>0</v>
+      </c>
+      <c r="I101" s="11">
         <v>0</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="102" customHeight="1" ht="15" spans="1:5">
+    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C102" s="13" t="n">
+      <c r="C102" s="13">
         <v>22230</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E102" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" ht="15" spans="1:1">
+      <c r="E102" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="104" customHeight="1" ht="20.4" spans="1:10">
+    <row r="104" spans="1:12" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>14</v>
       </c>
@@ -2795,29 +3174,29 @@
       <c r="C104" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D104" s="8" t="n">
+      <c r="D104" s="8">
         <v>495000</v>
       </c>
-      <c r="E104" s="9" t="n">
+      <c r="E104" s="9">
         <v>0.39</v>
       </c>
-      <c r="F104" s="9" t="n">
+      <c r="F104" s="9">
         <v>193050</v>
       </c>
       <c r="G104" s="10">
-        <v>46273.7581365741</v>
-      </c>
-      <c r="H104" s="8" t="n">
+        <v>46273.758136574099</v>
+      </c>
+      <c r="H104" s="8">
         <v>260000</v>
       </c>
-      <c r="I104" s="11" t="n">
+      <c r="I104" s="11">
         <v>52.53</v>
       </c>
       <c r="J104" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="105" customHeight="1" ht="37.9" spans="1:10">
+    <row r="105" spans="1:12" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>14</v>
       </c>
@@ -2827,51 +3206,51 @@
       <c r="C105" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D105" s="8" t="n">
+      <c r="D105" s="8">
         <v>5000</v>
       </c>
-      <c r="E105" s="9" t="n">
+      <c r="E105" s="9">
         <v>0.39</v>
       </c>
-      <c r="F105" s="9" t="n">
+      <c r="F105" s="9">
         <v>1950</v>
       </c>
       <c r="G105" s="10">
         <v>46273</v>
       </c>
-      <c r="H105" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="11" t="n">
+      <c r="H105" s="8">
+        <v>0</v>
+      </c>
+      <c r="I105" s="11">
         <v>0</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="106" customHeight="1" ht="15" spans="1:5">
+    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B106" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C106" s="13" t="n">
+      <c r="C106" s="13">
         <v>195000</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E106" s="14" t="n">
+      <c r="E106" s="14">
         <v>260000</v>
       </c>
     </row>
-    <row r="107" customHeight="1" ht="77.35" spans="1:1">
+    <row r="107" spans="1:12" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="108" customHeight="1" ht="15" spans="1:12">
+    <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>1</v>
       </c>
@@ -2909,12 +3288,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" customHeight="1" ht="15" spans="1:1">
+    <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="110" customHeight="1" ht="30.35" spans="1:10">
+    <row r="110" spans="1:12" ht="30.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>14</v>
       </c>
@@ -2924,47 +3303,47 @@
       <c r="C110" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D110" s="8" t="n">
+      <c r="D110" s="8">
         <v>5000</v>
       </c>
-      <c r="E110" s="9" t="n">
+      <c r="E110" s="9">
         <v>15.75</v>
       </c>
-      <c r="F110" s="9" t="n">
+      <c r="F110" s="9">
         <v>78750</v>
       </c>
       <c r="G110" s="10">
         <v>46275</v>
       </c>
-      <c r="H110" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="11" t="n">
+      <c r="H110" s="8">
+        <v>0</v>
+      </c>
+      <c r="I110" s="11">
         <v>0</v>
       </c>
       <c r="J110" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="111" customHeight="1" ht="15" spans="1:5">
+    <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C111" s="13" t="n">
+      <c r="C111" s="13">
         <v>78750</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E111" s="14" t="n">
+      <c r="E111" s="14">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins header="0" footer="0" left="0.25" top="0.25" right="0" bottom="0.25"/>
-  <pageSetup firstPageNo="1" scale="0" orientation="landscape" paperSize="9"/>
+  <pageMargins left="0.25" right="0" top="0.25" bottom="0.25" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="0" orientation="landscape"/>
 </worksheet>
 </file>